--- a/Resources/entity_template.xlsx
+++ b/Resources/entity_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaewo\Desktop\work\mapper\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7B9C86-0120-4CEE-B239-2BA1249C832B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAA2E10-111E-4DE7-83D7-56DD1F462663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="948" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="948" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity 작성요령" sheetId="33" r:id="rId1"/>
@@ -1442,7 +1442,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1679,6 +1679,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6753,7 +6756,7 @@
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="E3" s="87"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
